--- a/artfynd/A 55814-2023 artfynd.xlsx
+++ b/artfynd/A 55814-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55814-2023 artfynd.xlsx
+++ b/artfynd/A 55814-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68128129</v>
+        <v>73778022</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rötjärnberget-Flakamyrberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720724.8384949099</v>
+        <v>720626</v>
       </c>
       <c r="R2" t="n">
-        <v>7084277.829338601</v>
+        <v>7084303</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-08-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-08-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Julia Pettersson, Anna Hallmén, Sören Uppsäll, Henrik Sporrong, Åsa Stenman, Emil Larsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73778022</v>
+        <v>73778040</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720625.897595266</v>
+        <v>720734</v>
       </c>
       <c r="R3" t="n">
-        <v>7084303.207291176</v>
+        <v>7084275</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +840,9 @@
           <t>2018-06-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-06-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,16 +872,11 @@
         <v>73778041</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -944,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720760.0123255614</v>
+        <v>720760</v>
       </c>
       <c r="R4" t="n">
-        <v>7084294.92658303</v>
+        <v>7084295</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,19 +937,9 @@
           <t>2018-06-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-06-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73778042</v>
+        <v>68128129</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,34 +977,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rötjärnberget-Flakamyrberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720799.8998461657</v>
+        <v>720725</v>
       </c>
       <c r="R5" t="n">
-        <v>7084326.976666774</v>
+        <v>7084278</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,22 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-06-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-06-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,57 +1061,57 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Julia Pettersson, Anna Hallmén, Sören Uppsäll, Henrik Sporrong, Åsa Stenman, Emil Larsson</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73778040</v>
+        <v>73778039</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rötjärnberget-Flakamyrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720733.9156728686</v>
+        <v>720708</v>
       </c>
       <c r="R6" t="n">
-        <v>7084274.924035527</v>
+        <v>7084273</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,19 +1141,9 @@
           <t>2018-06-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-06-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,123 +1167,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>73778039</v>
-      </c>
-      <c r="B7" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Rötjärnberget-Flakamyrberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>720707.8705207512</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7084273.090349836</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2018-06-12</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2018-06-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Julia Pettersson, Anna Hallmén, Sören Uppsäll, Henrik Sporrong, Åsa Stenman, Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55814-2023 artfynd.xlsx
+++ b/artfynd/A 55814-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778022</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778040</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778041</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68128129</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,8 +1192,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73778039</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>